--- a/diseases/d170/2026-2029.xlsx
+++ b/diseases/d170/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1217,6 +1232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1362,6 +1382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1507,6 +1532,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1652,6 +1682,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1795,6 +1830,11 @@
       <c r="S9" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">

--- a/diseases/d170/2026-2029.xlsx
+++ b/diseases/d170/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.04345692446436896</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,23 +783,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0.02172846223218448</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,23 +921,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0.04780261691080586</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,23 +1059,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1227,11 +1182,6 @@
       <c r="R5" t="n">
         <v>0.01303707733931069</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1244,23 +1194,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1377,11 +1317,6 @@
       <c r="R6" t="n">
         <v>0.004345692446436896</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1394,23 +1329,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1527,11 +1452,6 @@
       <c r="R7" t="n">
         <v>0.01738276978574758</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1544,23 +1464,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1677,11 +1587,6 @@
       <c r="R8" t="n">
         <v>0.03041984712505827</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1694,23 +1599,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1827,11 +1722,6 @@
       <c r="R9" t="n">
         <v>0.004345692446436896</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1844,22 +1734,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
